--- a/sheets/조재수대금교본/검수/인연.xlsx
+++ b/sheets/조재수대금교본/검수/인연.xlsx
@@ -3594,7 +3594,7 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -3605,11 +3605,7 @@
         </is>
       </c>
       <c r="M3" s="22"/>
-      <c r="N3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N3" s="21"/>
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
@@ -3664,11 +3660,7 @@
     </row>
     <row r="5" ht="119.22" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B5" s="21"/>
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
@@ -3678,8 +3670,7 @@
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∼
-‹</t>
+          <t xml:space="preserve">湳∼</t>
         </is>
       </c>
       <c r="G5" s="24"/>
@@ -3689,16 +3680,11 @@
         </is>
       </c>
       <c r="I5" s="24"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="M5" s="24"/>
@@ -3724,8 +3710,7 @@
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞
-ﾉ</t>
+㳞</t>
         </is>
       </c>
       <c r="E6" s="22"/>
@@ -3739,8 +3724,7 @@
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞
-‹</t>
+㳞</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -3753,9 +3737,8 @@
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ﾉ
-–
-仲林∧</t>
+          <t xml:space="preserve">–
+仲林</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -3784,13 +3767,13 @@
       <c r="C7" s="23"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G7" s="23"/>
@@ -3809,7 +3792,7 @@
       <c r="K7" s="23"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲∽</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="M7" s="23"/>
@@ -3879,16 +3862,11 @@
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="C9" s="22"/>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D9" s="21"/>
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
@@ -3904,11 +3882,7 @@
         </is>
       </c>
       <c r="K9" s="22"/>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L9" s="21"/>
       <c r="M9" s="22"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
@@ -3923,8 +3897,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ﾉ
-–
+          <t xml:space="preserve">–
 汰潢</t>
         </is>
       </c>
@@ -3943,16 +3916,11 @@
         </is>
       </c>
       <c r="G10" s="23"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⌝</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K10" s="23"/>
@@ -3966,8 +3934,7 @@
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="O10" s="23"/>
@@ -3983,7 +3950,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C11" s="24"/>
@@ -3995,7 +3962,7 @@
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G11" s="24"/>
@@ -4007,13 +3974,13 @@
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -4079,11 +4046,7 @@
         </is>
       </c>
       <c r="E13" s="23"/>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F13" s="21"/>
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
@@ -4092,11 +4055,7 @@
         </is>
       </c>
       <c r="I13" s="23"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J13" s="21"/>
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
@@ -4104,11 +4063,7 @@
         </is>
       </c>
       <c r="M13" s="23"/>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N13" s="21"/>
       <c r="O13" s="23"/>
       <c r="P13" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/인연.xlsx
+++ b/sheets/조재수대금교본/검수/인연.xlsx
@@ -3594,7 +3594,7 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -3605,7 +3605,11 @@
         </is>
       </c>
       <c r="M3" s="22"/>
-      <c r="N3" s="21"/>
+      <c r="N3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
@@ -3710,7 +3714,8 @@
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞</t>
+㳞
+ﾉ</t>
         </is>
       </c>
       <c r="E6" s="22"/>
@@ -3737,8 +3742,9 @@
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-仲林</t>
+          <t xml:space="preserve">ﾉ
+–
+仲林∧</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -3767,13 +3773,13 @@
       <c r="C7" s="23"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="G7" s="23"/>
@@ -3792,7 +3798,7 @@
       <c r="K7" s="23"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲∽</t>
         </is>
       </c>
       <c r="M7" s="23"/>
@@ -3862,7 +3868,7 @@
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="C9" s="22"/>
@@ -3897,7 +3903,8 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
+          <t xml:space="preserve">ﾉ
+–
 汰潢</t>
         </is>
       </c>
@@ -3920,7 +3927,8 @@
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+⌝</t>
         </is>
       </c>
       <c r="K10" s="23"/>
@@ -3950,7 +3958,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="C11" s="24"/>
@@ -3962,7 +3970,7 @@
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="G11" s="24"/>
@@ -3974,13 +3982,13 @@
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -4063,7 +4071,11 @@
         </is>
       </c>
       <c r="M13" s="23"/>
-      <c r="N13" s="21"/>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O13" s="23"/>
       <c r="P13" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/인연.xlsx
+++ b/sheets/조재수대금교본/검수/인연.xlsx
@@ -3522,28 +3522,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="80.0" customHeight="true">
+    <row r="2" ht="74.07" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="119.22" customHeight="true">
+    <row r="3" ht="110.36" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="119.22" customHeight="true">
+    <row r="4" ht="110.36" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="119.22" customHeight="true">
+    <row r="5" ht="110.36" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="119.22" customHeight="true">
+    <row r="6" ht="110.36" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="119.22" customHeight="true">
+    <row r="7" ht="110.36" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="119.22" customHeight="true">
+    <row r="8" ht="110.36" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="119.22" customHeight="true">
+    <row r="9" ht="110.36" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
       <c r="P9" s="21"/>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="119.22" customHeight="true">
+    <row r="10" ht="110.36" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="119.22" customHeight="true">
+    <row r="11" ht="110.36" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="119.22" customHeight="true">
+    <row r="12" ht="110.36" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="119.22" customHeight="true">
+    <row r="13" ht="110.36" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="119.22" customHeight="true">
+    <row r="14" ht="110.36" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4149,6 +4149,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="54"/>
 </worksheet>
 </file>